--- a/tests/E77-915M30S/E77-915M30S.xlsx
+++ b/tests/E77-915M30S/E77-915M30S.xlsx
@@ -5,10 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1_RX" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="1_TX_5V" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,12 +21,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t xml:space="preserve">F, MHz</t>
   </si>
   <si>
     <t xml:space="preserve">RSSI, dBm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F=915 MHz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U=5,08V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I, A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pset=16 dBm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U,V</t>
   </si>
 </sst>
 </file>
@@ -249,7 +271,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>1_RX!$A$14:$A$54</c:f>
+              <c:f>'1_RX'!$A$14:$A$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="41"/>
@@ -381,7 +403,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>1_RX!$C$14:$C$54</c:f>
+              <c:f>'1_RX'!$C$14:$C$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="41"/>
@@ -513,11 +535,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="67392593"/>
-        <c:axId val="17029854"/>
+        <c:axId val="22828006"/>
+        <c:axId val="10044147"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="67392593"/>
+        <c:axId val="22828006"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -546,12 +568,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17029854"/>
+        <c:crossAx val="10044147"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="17029854"/>
+        <c:axId val="10044147"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -589,7 +611,660 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67392593"/>
+        <c:crossAx val="22828006"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="B3B3B3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="span"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:scatterChart>
+        <c:scatterStyle val="line"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>p_out</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>p_out</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28800">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'1_TX_5V'!$A$3:$A$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>-9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>17</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'1_TX_5V'!$B$3:$B$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>11.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>17.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20.7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>22.7</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>23.3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>25.2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>26.4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>27.1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>27.6</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>27.8</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>28.1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>28.2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>28.6</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>28.6</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>28.7</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>28.7</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>28.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="90077027"/>
+        <c:axId val="55697821"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="90077027"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="B3B3B3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="55697821"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="55697821"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="B3B3B3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="B3B3B3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="90077027"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="B3B3B3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="span"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:scatterChart>
+        <c:scatterStyle val="line"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28800">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'1_TX_5V'!$A$32:$A$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'1_TX_5V'!$B$32:$B$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>26.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>28.6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>28.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>29</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="27739223"/>
+        <c:axId val="8189561"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="27739223"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="B3B3B3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="8189561"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="8189561"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="B3B3B3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="B3B3B3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="27739223"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -644,7 +1319,439 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarkerLayout>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarkerLayout>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -881,6 +1988,71 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>723960</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>143640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>793080</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>134280</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3162240" y="468720"/>
+        <a:ext cx="5758920" cy="3241800"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>29880</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>66960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>99000</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>57240</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3281040" y="4131000"/>
+        <a:ext cx="5758920" cy="3241440"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1652,7 +2824,519 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;CСторінка &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>-9</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <f aca="false">A3+1</f>
+        <v>-8</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <f aca="false">A4+1</f>
+        <v>-7</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <f aca="false">A5+1</f>
+        <v>-6</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <f aca="false">A6+1</f>
+        <v>-5</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <f aca="false">A7+1</f>
+        <v>-4</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <f aca="false">A8+1</f>
+        <v>-3</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <f aca="false">A9+1</f>
+        <v>-2</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <f aca="false">A10+1</f>
+        <v>-1</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <f aca="false">A11+1</f>
+        <v>0</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
+        <f aca="false">A12+1</f>
+        <v>1</v>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
+        <f aca="false">A13+1</f>
+        <v>2</v>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
+        <f aca="false">A14+1</f>
+        <v>3</v>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="n">
+        <f aca="false">A15+1</f>
+        <v>4</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
+        <f aca="false">A16+1</f>
+        <v>5</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="n">
+        <f aca="false">A17+1</f>
+        <v>6</v>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
+        <f aca="false">A18+1</f>
+        <v>7</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="n">
+        <f aca="false">A19+1</f>
+        <v>8</v>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="n">
+        <f aca="false">A20+1</f>
+        <v>9</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
+        <f aca="false">A21+1</f>
+        <v>10</v>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="n">
+        <f aca="false">A22+1</f>
+        <v>11</v>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="n">
+        <f aca="false">A23+1</f>
+        <v>12</v>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="n">
+        <f aca="false">A24+1</f>
+        <v>13</v>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="n">
+        <f aca="false">A25+1</f>
+        <v>14</v>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="n">
+        <f aca="false">A26+1</f>
+        <v>15</v>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="n">
+        <f aca="false">A27+1</f>
+        <v>16</v>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="n">
+        <f aca="false">A28+1</f>
+        <v>17</v>
+      </c>
+      <c r="B29" s="0" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="n">
+        <f aca="false">A32+0.2</f>
+        <v>3.6</v>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="n">
+        <f aca="false">A33+0.2</f>
+        <v>3.8</v>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="n">
+        <f aca="false">A34+0.2</f>
+        <v>4</v>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="n">
+        <f aca="false">A35+0.2</f>
+        <v>4.2</v>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="n">
+        <f aca="false">A36+0.2</f>
+        <v>4.4</v>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="n">
+        <f aca="false">A37+0.2</f>
+        <v>4.6</v>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="n">
+        <f aca="false">A38+0.2</f>
+        <v>4.8</v>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="n">
+        <f aca="false">A39+0.2</f>
+        <v>5</v>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="C40" s="0" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="n">
+        <f aca="false">A40+0.2</f>
+        <v>5.2</v>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="n">
+        <f aca="false">A41+0.2</f>
+        <v>5.4</v>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="C42" s="0" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CСторінка &amp;P</oddFooter>
